--- a/artfynd/A 27521-2026 artfynd.xlsx
+++ b/artfynd/A 27521-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129920357</v>
+        <v>129920364</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ytterbäcken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730498</v>
+        <v>730503</v>
       </c>
       <c r="R2" t="n">
-        <v>7123083</v>
+        <v>7123061</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129920365</v>
+        <v>131118184</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ytterbäcken, Vb</t>
+          <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730559</v>
+        <v>730201</v>
       </c>
       <c r="R3" t="n">
-        <v>7123003</v>
+        <v>7123326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129920364</v>
+        <v>129920365</v>
       </c>
       <c r="B4" t="n">
-        <v>91770</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730503</v>
+        <v>730559</v>
       </c>
       <c r="R4" t="n">
-        <v>7123061</v>
+        <v>7123003</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +969,7 @@
         <v>129920356</v>
       </c>
       <c r="B5" t="n">
-        <v>83199</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,11 +1066,11 @@
         <v>129920358</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1176,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131118184</v>
+        <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>91844</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730201</v>
+        <v>730393</v>
       </c>
       <c r="R7" t="n">
-        <v>7123326</v>
+        <v>7123085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131118183</v>
+        <v>129920357</v>
       </c>
       <c r="B8" t="n">
-        <v>57911</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,16 +1268,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1301,17 +1285,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Lidmyran, Vb</t>
+          <t>Ytterbäcken, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730393</v>
+        <v>730498</v>
       </c>
       <c r="R8" t="n">
-        <v>7123085</v>
+        <v>7123083</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,6 +1367,518 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129920359</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ytterbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>730499</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7123296</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129920360</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ytterbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>730501</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7123291</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129920361</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ytterbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>730504</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7123286</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129303592</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>730503</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7122959</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129920362</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ytterbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>730472</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7123350</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27521-2026 artfynd.xlsx
+++ b/artfynd/A 27521-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118184</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920364</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920356</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920358</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118183</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920357</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920359</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920360</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,6 +1723,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920361</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1782,6 +1837,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129303592</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,8 +1939,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920362</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>